--- a/artfynd/A 13467-2024 artfynd.xlsx
+++ b/artfynd/A 13467-2024 artfynd.xlsx
@@ -1849,11 +1849,11 @@
         <v>119442569</v>
       </c>
       <c r="B13" t="n">
-        <v>57421</v>
+        <v>57601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/artfynd/A 13467-2024 artfynd.xlsx
+++ b/artfynd/A 13467-2024 artfynd.xlsx
@@ -1849,7 +1849,7 @@
         <v>119442569</v>
       </c>
       <c r="B13" t="n">
-        <v>57601</v>
+        <v>57602</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13467-2024 artfynd.xlsx
+++ b/artfynd/A 13467-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119442909</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119442721</v>
+        <v>119442359</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748826</v>
+        <v>748833</v>
       </c>
       <c r="R3" t="n">
-        <v>7154568</v>
+        <v>7154607</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,43 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119442385</v>
+        <v>119442582</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748833</v>
+        <v>748785</v>
       </c>
       <c r="R4" t="n">
-        <v>7154607</v>
+        <v>7154632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119442915</v>
+        <v>119442602</v>
       </c>
       <c r="B5" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748855</v>
+        <v>748815</v>
       </c>
       <c r="R5" t="n">
-        <v>7154574</v>
+        <v>7154582</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119442359</v>
+        <v>119442721</v>
       </c>
       <c r="B6" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748833</v>
+        <v>748826</v>
       </c>
       <c r="R6" t="n">
-        <v>7154607</v>
+        <v>7154568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119442855</v>
+        <v>119442832</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,31 +1191,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1254,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748819</v>
+        <v>748902</v>
       </c>
       <c r="R7" t="n">
-        <v>7154579</v>
+        <v>7154544</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,6 +1262,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119442417</v>
+        <v>119442915</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>748818</v>
+        <v>748855</v>
       </c>
       <c r="R8" t="n">
-        <v>7154626</v>
+        <v>7154574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,19 +1382,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119442425</v>
+        <v>119442395</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1465,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>748799</v>
+        <v>748844</v>
       </c>
       <c r="R9" t="n">
-        <v>7154623</v>
+        <v>7154636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119442746</v>
+        <v>119442404</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>748815</v>
+        <v>748821</v>
       </c>
       <c r="R10" t="n">
-        <v>7154556</v>
+        <v>7154612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119442602</v>
+        <v>119442417</v>
       </c>
       <c r="B11" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>748815</v>
+        <v>748818</v>
       </c>
       <c r="R11" t="n">
-        <v>7154582</v>
+        <v>7154626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,19 +1685,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119442591</v>
+        <v>119442425</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1783,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>748771</v>
+        <v>748799</v>
       </c>
       <c r="R12" t="n">
-        <v>7154603</v>
+        <v>7154623</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,51 +1786,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119442569</v>
+        <v>119442591</v>
       </c>
       <c r="B13" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1898,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>748794</v>
+        <v>748771</v>
       </c>
       <c r="R13" t="n">
-        <v>7154627</v>
+        <v>7154603</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,6 +1868,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1960,42 +1887,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119442582</v>
+        <v>119442798</v>
       </c>
       <c r="B14" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2003,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>748785</v>
+        <v>748901</v>
       </c>
       <c r="R14" t="n">
-        <v>7154632</v>
+        <v>7154532</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,15 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119442404</v>
+        <v>119442855</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,26 +2003,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2109,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>748821</v>
+        <v>748819</v>
       </c>
       <c r="R15" t="n">
-        <v>7154612</v>
+        <v>7154579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2079,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2169,6 +2094,217 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>119442569</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Eliasgrovliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>748794</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7154627</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119442385</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eliasgrovliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>748833</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7154607</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13467-2024 artfynd.xlsx
+++ b/artfynd/A 13467-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442909</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442359</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442582</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442602</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442721</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442832</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442915</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442395</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442404</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442417</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442425</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442591</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442798</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,6 +2164,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442855</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442569</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2305,8 +2385,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442385</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>